--- a/eventos/sap-now-2026/checklist-sap-now-2026.xlsx
+++ b/eventos/sap-now-2026/checklist-sap-now-2026.xlsx
@@ -2606,14 +2606,14 @@
       <c r="E6" s="5" t="inlineStr"/>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>R$ 41,63/un — UV direto 5,6cm — renan@cuberbrasil.com</t>
+          <t>R$ 41,63/un — UV direto 5,6cm — renan@cuberbrasil.com / (19) 99606-4010</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Brindes — Embalagem personalizada</t>
+          <t>Brindes — Bloco notas cubo BL31 (250 un.)</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -2621,14 +2621,14 @@
           <t>A definir</t>
         </is>
       </c>
-      <c r="C7" s="15" t="n">
-        <v>0</v>
+      <c r="C7" s="12" t="n">
+        <v>8767.5</v>
       </c>
       <c r="D7" s="8" t="inlineStr"/>
       <c r="E7" s="8" t="inlineStr"/>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>A orçar</t>
+          <t>R$ 35,07/un — 95x95x95mm, sik screen, azul. Fornecedor a fechar</t>
         </is>
       </c>
     </row>
@@ -3069,7 +3069,7 @@
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Embalagem personalizada</t>
+          <t>BL31 - Bloco notas cubo papelão reciclado</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -3095,13 +3095,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="8" t="inlineStr"/>
+      <c r="G7" s="12" t="n">
+        <v>35.07</v>
+      </c>
+      <c r="H7" s="12" t="n">
+        <v>8767.5</v>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>5 blocos autocolantes 7,5x7,5cm + sticky notes + porta canetas. Azul. 95x95x95mm. Sik screen 01 cor. NCM 48202000</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="5" t="inlineStr">

--- a/eventos/sap-now-2026/checklist-sap-now-2026.xlsx
+++ b/eventos/sap-now-2026/checklist-sap-now-2026.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cotações Brindes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Checklist SAP NOW 2026'!$A$2:$E$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Checklist SAP NOW 2026'!$A$2:$E$108</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -54,7 +54,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -78,7 +78,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEBEE"/>
+        <fgColor rgb="00C8E6C9"/>
       </patternFill>
     </fill>
     <fill>
@@ -88,12 +88,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EBF5FB"/>
+        <fgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C8E6C9"/>
+        <fgColor rgb="00FFEBEE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EBF5FB"/>
       </patternFill>
     </fill>
   </fills>
@@ -123,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -149,16 +154,22 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -167,16 +178,16 @@
     <xf numFmtId="164" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -544,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E92"/>
+  <dimension ref="A1:E107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -557,7 +568,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CHECKLIST SAP NOW AI TOUR 2026  —  09 e 10/set  |  Transamérica Expo Center</t>
+          <t>CHECKLIST SAP NOW AI TOUR 2026  —  09 e 10/set  |  Transamérica Expo Center  |  Estande 03</t>
         </is>
       </c>
     </row>
@@ -598,17 +609,17 @@
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Acompanhar formulário enviado para SAP</t>
+          <t>Fechamento do contrato</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>30/jun</t>
+          <t>31/dez</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Ok</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -621,17 +632,17 @@
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Data final para envio dos conteúdos para a agenda (sessão Klabin)</t>
+          <t>Acesso ao manual do expositor</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>26/jun</t>
+          <t>20/mai</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Ok</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -639,26 +650,22 @@
           <t>Fran</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>CRÍTICO — prazo fixo SAP</t>
-        </is>
-      </c>
+      <c r="E5" s="7" t="inlineStr"/>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Definir ativações e brindes</t>
+          <t>Envio de logomarca para organizadora para site</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>22/jun</t>
+          <t>29/mai</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Ok</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -666,22 +673,26 @@
           <t>Fran</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr"/>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Fundo branco, 1920x1080px. Formatos: PNG ou JPG</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Orçamento stand com a agência</t>
+          <t>Breve descritivo da empresa</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>10/jun</t>
+          <t>29/mai</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Ok</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -691,24 +702,24 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>Texto até 400 caracteres + logotipo da empresa</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Planejar anúncios de geolocalização durante os dias do evento</t>
+          <t>Envio de logomarca para impressão</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>30/jun</t>
+          <t>24/jun</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Ok</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -716,22 +727,26 @@
           <t>Fran</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Vetor (.ai ou .eps, CMYK), fontes convertidas em curvas</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Enviar assinatura do orçamento de anúncios SAP NOW 2026 (P/Hotéis) Eletromidia</t>
+          <t>Solicitação para agência nossa logo para o site</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>30/jun</t>
+          <t>29/mai</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Ok</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -744,17 +759,17 @@
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Prazo final para envio das artes exclusivas de acordo com as cotas adquiridas</t>
+          <t>Solicitação para agência nossa logo para a impressão</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>15/jul</t>
+          <t>29/mai</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Ok</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -767,17 +782,17 @@
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Aguardando NF para pagamento dos serviços e equipamentos</t>
+          <t>Solicitar 2 Coletores de dados</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>15/jul</t>
+          <t>15/jun</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Ok</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -785,22 +800,26 @@
           <t>Fran</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr"/>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>R$ 577,72 (2x) = Solicitado em 10/06/26</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Criar anúncios de geolocalização durante os dias do evento</t>
+          <t>Cartão de visita</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>15/jul</t>
+          <t>10/jun</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Ok</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -813,7 +832,7 @@
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Vídeo do anúncio para SAP NOW 2026 (P/Hotéis)</t>
+          <t>Aprovar orçamento de anúncios para SAP NOW 2026 (P/Hotéis)</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
@@ -823,7 +842,7 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Ok</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -836,17 +855,17 @@
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Envio das artes do stand</t>
+          <t>Solicitar assinatura do orçamento de anúncios para SAP NOW 2026 (P/Hotéis)</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>15/jul</t>
+          <t>20/jun</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Ok</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -859,17 +878,17 @@
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Camisetas para equipe</t>
+          <t>Criar cadência de reuniões com sócios</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>10/jul</t>
+          <t>05/set</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Ok</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -877,70 +896,70 @@
           <t>Fran</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>27 camisetas + 12 polos</t>
-        </is>
-      </c>
+      <c r="E15" s="7" t="inlineStr"/>
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Envio dos pedidos de aprovação de ativações e brindes para SAP</t>
+          <t>Definir sessão principal 1ª escolha: Klabin</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>30/jul</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+          <t>30/mai</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Em andamento</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr"/>
+          <t>Sócios</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Klabin</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Prazo final para pagamento de serviços e equipamentos</t>
+          <t>Formulário de sessão principal — enviar para a SAP (1ª escolha: TBD)</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>30/jul</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr"/>
+          <t>06/jun</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Em andamento</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr"/>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>Klabin, enviar para a SAP</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Prazo final para envio dos pedidos de aprovação de ativações e brindes</t>
+          <t>Acompanhar formulário enviado para SAP</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>31/jul</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
+          <t>30/jun</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -950,20 +969,20 @@
           <t>Fran</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>CRÍTICO — prazo fixo SAP</t>
-        </is>
-      </c>
+      <c r="E18" s="4" t="inlineStr"/>
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>Layout do stand</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr"/>
-      <c r="C19" s="6" t="inlineStr">
+          <t>Prazo final para pagamento de serviços e equipamentos</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>30/jul</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -978,11 +997,15 @@
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Pgto stand layout da agência</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr"/>
-      <c r="C20" s="6" t="inlineStr">
+          <t>Aguardando NF para pagamento dos serviços e equipamentos</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>15/jul</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -997,11 +1020,15 @@
     <row r="21" ht="28" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>Criação das artes do DOOH</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr"/>
-      <c r="C21" s="6" t="inlineStr">
+          <t>Aprovação de arte Plaquinha estande</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>07/ago</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -1016,11 +1043,15 @@
     <row r="22" ht="28" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Aprovação das artes do DOOH</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr"/>
-      <c r="C22" s="6" t="inlineStr">
+          <t>Envio dos pedidos de aprovação de ativações e brindes para SAP</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>30/jul</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -1035,11 +1066,15 @@
     <row r="23" ht="28" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>Burocracias da participação (taxa de prefeitura)</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr"/>
-      <c r="C23" s="6" t="inlineStr">
+          <t>Confirmação de data e horário da palestra</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>01/ago</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -1049,16 +1084,24 @@
           <t>Fran</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr"/>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>Sessão Klabin — data TBD</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="28" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Adaptador de rede para PC</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr"/>
-      <c r="C24" s="6" t="inlineStr">
+          <t>Prazo final para envio das artes exclusivas de acordo com as cotas adquiridas</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>15/jul</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -1073,11 +1116,15 @@
     <row r="25" ht="28" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>TV + suporte + cabos</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr"/>
-      <c r="C25" s="6" t="inlineStr">
+          <t>Definir ativações e brindes</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>22/jun</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -1092,34 +1139,38 @@
     <row r="26" ht="28" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>1 Tablet e peças para demo</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr"/>
-      <c r="C26" s="6" t="inlineStr">
+          <t>Prazo final para envio dos pedidos de aprovação de ativações e brindes</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>31/jul</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Andrey</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr"/>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>CRÍTICO — prazo fixo SAP</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="28" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Confirmação de data e horário da palestra</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>01/ago</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
+          <t>Burocracias da participação (taxa de prefeitura)</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr"/>
+      <c r="C27" s="10" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -1129,24 +1180,20 @@
           <t>Fran</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>Sessão Klabin — data TBD</t>
-        </is>
-      </c>
+      <c r="E27" s="7" t="inlineStr"/>
     </row>
     <row r="28" ht="28" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Vídeos para TV principal</t>
+          <t>Data final para envio dos conteúdos para a agenda</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>01/ago</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
+          <t>26/jun</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -1158,29 +1205,29 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>R$ 5.280,00 — SAP com LCA estará no evento</t>
+          <t>CRÍTICO — prazo fixo SAP</t>
         </is>
       </c>
     </row>
     <row r="29" ht="28" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>Pedir hotel evento para time</t>
+          <t>Data final de Inscrição de Credencial do patrocinador</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>01/ago</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
+          <t>28/ago</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Viviane</t>
+          <t>Fran</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr"/>
@@ -1188,22 +1235,22 @@
     <row r="30" ht="28" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Aprovação de arte Plaquinha estande</t>
+          <t>Envio de report com os inscritos da Solveplan</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>07/ago</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
+          <t>11/set</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Fran</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr"/>
@@ -1211,38 +1258,42 @@
     <row r="31" ht="28" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>Ir na SVPL pegar materiais e brindes</t>
+          <t>Retirada de coletor de dados — CAEX</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>08/ago</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
+          <t>08/set</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Andrey</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr"/>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>RedDoor — R$ 1.601,14</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="28" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Recebimento camisetas</t>
+          <t>Credenciais: Definir time que irá ao evento</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>10/ago</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
+          <t>15/ago</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -1252,16 +1303,24 @@
           <t>Fran</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr"/>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>8 credenciais + 1 staff</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="28" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>Finalização apresentação do Cliente</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="inlineStr"/>
-      <c r="C33" s="6" t="inlineStr">
+          <t>Vídeos para TV principal</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>01/ago</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -1271,16 +1330,24 @@
           <t>Fran</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr"/>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>R$ 5.280,00 — SAP com LCA estará no evento</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="28" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Enviar apresentação do Cliente para SAP</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr"/>
-      <c r="C34" s="6" t="inlineStr">
+          <t>Credenciamento de montagem</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>04/set</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -1295,15 +1362,11 @@
     <row r="35" ht="28" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>Criar arte para display de balcão com QR Code</t>
-        </is>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>15/ago</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
+          <t>Finalização apresentação do Cliente</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr"/>
+      <c r="C35" s="10" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -1318,65 +1381,57 @@
     <row r="36" ht="28" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Definir clientes a serem convidados (até 10)</t>
+          <t>Enviar apresentação do Cliente para SAP</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr"/>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C36" s="10" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Sócios</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>Klabin, Aço Cearense, Citrosuco, Eurofarma, Grupo Comporte, M. Dias Branco, Usina da Pedra, Cocal, Zaffari, MarcoPolo</t>
-        </is>
-      </c>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr"/>
     </row>
     <row r="37" ht="28" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>Credenciais: Definir time que irá ao evento</t>
+          <t>Pedir hotel evento para time</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>15/ago</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
+          <t>01/ago</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>8 credenciais + 1 staff</t>
-        </is>
-      </c>
+          <t>Viviane</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr"/>
     </row>
     <row r="38" ht="28" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Data final de Inscrição de Credencial do patrocinador</t>
+          <t>Criar arte para display de balcão com QR Code</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>28/ago</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
+          <t>15/ago</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -1391,38 +1446,38 @@
     <row r="39" ht="28" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>Recebimento Brindes</t>
+          <t>Definir clientes a serem convidados (até 10)</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr"/>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C39" s="10" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Fran</t>
+          <t>Sócios</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>Cubo Mágico A Cuber Brasil — R$10.407,50</t>
+          <t>Klabin, Aço Cearense, Citrosuco, Eurofarma, Grupo Comporte, M. Dias Branco, Usina da Pedra, Cocal, Zaffari, MarcoPolo</t>
         </is>
       </c>
     </row>
     <row r="40" ht="28" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Credenciamento de montagem</t>
+          <t>Planejar anúncios de geolocalização durante os dias do evento</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>04/set</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
+          <t>30/jun</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -1437,42 +1492,38 @@
     <row r="41" ht="28" customHeight="1">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>Retirada de credencial</t>
+          <t>Criar anúncios de geolocalização durante os dias do evento</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>08/set</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
+          <t>15/jul</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Todos</t>
-        </is>
-      </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>CAEX 08h-14h ou 09/set das 7h-18h</t>
-        </is>
-      </c>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr"/>
     </row>
     <row r="42" ht="28" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Retirada de coletor de dados — CAEX</t>
+          <t>Enviar assinatura do orçamento de anúncios para SAP NOW 2026 (P/Hotéis) p/ Eletromidia</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>08/set</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
+          <t>30/jun</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -1482,442 +1533,485 @@
           <t>Fran</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>RedDoor — R$ 1.601,14</t>
-        </is>
-      </c>
+      <c r="E42" s="4" t="inlineStr"/>
     </row>
     <row r="43" ht="28" customHeight="1">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>Envio de report com os inscritos da Solveplan</t>
+          <t>Vídeo do anúncio para SAP NOW 2026 (P/Hotéis)</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>11/set</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
+          <t>15/jul</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Fran</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr"/>
     </row>
-    <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Retirada de credencial</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>08/set</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>CAEX 08h-14h ou 09/set das 7h-18h</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>Ir na SVPL pegar materiais e brindes</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>08/ago</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr"/>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Adaptador de rede para PC</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr"/>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr"/>
+    </row>
+    <row r="47" ht="28" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>TV + suporte + cabos</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr"/>
+      <c r="C47" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr"/>
+    </row>
+    <row r="48" ht="28" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>1 Tablet e peças para demo</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr"/>
+      <c r="C48" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr"/>
+    </row>
+    <row r="49" ht="28" customHeight="1">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>Layout do stand</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr"/>
+      <c r="C49" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr"/>
+    </row>
+    <row r="50" ht="28" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Orçamento stand com a agência</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>10/jun</t>
+        </is>
+      </c>
+      <c r="C50" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>Pgto stand layout da agência</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr"/>
+      <c r="C51" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr"/>
+    </row>
+    <row r="52" ht="28" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Criação das artes do DOOH</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr"/>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr"/>
+    </row>
+    <row r="53" ht="28" customHeight="1">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>Aprovação das artes do DOOH</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr"/>
+      <c r="C53" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr"/>
+    </row>
+    <row r="54" ht="28" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Envio das artes do stand</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>15/jul</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr"/>
+    </row>
+    <row r="55" ht="28" customHeight="1">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>Camisetas para equipe</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>10/jul</t>
+        </is>
+      </c>
+      <c r="C55" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>27 camisetas + 12 polos</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="28" customHeight="1">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Recebimento camisetas</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>10/ago</t>
+        </is>
+      </c>
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr"/>
+    </row>
+    <row r="57" ht="28" customHeight="1">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>Recebimento Brindes</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr"/>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>Cubo Mágico A Cuber Brasil — R$10.407,50</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="28" customHeight="1">
+      <c r="A58" s="4" t="inlineStr"/>
+      <c r="B58" s="5" t="inlineStr"/>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr"/>
+      <c r="E58" s="4" t="inlineStr"/>
+    </row>
+    <row r="59" ht="28" customHeight="1">
+      <c r="A59" s="7" t="inlineStr"/>
+      <c r="B59" s="8" t="inlineStr"/>
+      <c r="C59" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr"/>
+      <c r="E59" s="7" t="inlineStr"/>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>COMUNICAÇÃO</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="3" t="inlineStr">
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>Atividade</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>Prazo</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="D62" s="3" t="inlineStr">
         <is>
           <t>Responsável</t>
         </is>
       </c>
-      <c r="E46" s="3" t="inlineStr">
+      <c r="E62" s="3" t="inlineStr">
         <is>
           <t>Obs.</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="28" customHeight="1">
-      <c r="A47" s="4" t="inlineStr">
+    <row r="63" ht="28" customHeight="1">
+      <c r="A63" s="4" t="inlineStr">
         <is>
           <t>Inicio dos convites</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr"/>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr"/>
-    </row>
-    <row r="48" ht="28" customHeight="1">
-      <c r="A48" s="7" t="inlineStr">
+      <c r="B63" s="5" t="inlineStr"/>
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr"/>
+    </row>
+    <row r="64" ht="28" customHeight="1">
+      <c r="A64" s="7" t="inlineStr">
         <is>
           <t>Enviar lista de convites para a SAP</t>
         </is>
       </c>
-      <c r="B48" s="8" t="inlineStr"/>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="E48" s="7" t="inlineStr">
+      <c r="B64" s="8" t="inlineStr"/>
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
         <is>
           <t>Prazo: 10/jul — 10 C-levels, máx. 2 por empresa</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="28" customHeight="1">
-      <c r="A49" s="4" t="inlineStr">
+    <row r="65" ht="28" customHeight="1">
+      <c r="A65" s="4" t="inlineStr">
         <is>
           <t>Página do evento no site</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr"/>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="inlineStr"/>
-    </row>
-    <row r="50" ht="28" customHeight="1">
-      <c r="A50" s="7" t="inlineStr">
+      <c r="B65" s="5" t="inlineStr"/>
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr"/>
+    </row>
+    <row r="66" ht="28" customHeight="1">
+      <c r="A66" s="7" t="inlineStr">
         <is>
           <t>Formulário para QR Code do stand</t>
         </is>
       </c>
-      <c r="B50" s="8" t="inlineStr"/>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="E50" s="7" t="inlineStr">
+      <c r="B66" s="8" t="inlineStr"/>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
         <is>
           <t>HubSpot form</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="28" customHeight="1">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>Fazer card para WhatsApp para convite</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr"/>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="inlineStr"/>
-    </row>
-    <row r="52" ht="28" customHeight="1">
-      <c r="A52" s="7" t="inlineStr">
-        <is>
-          <t>Reunião com AEs, sócios e líderes de kickoff</t>
-        </is>
-      </c>
-      <c r="B52" s="8" t="inlineStr"/>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="E52" s="7" t="inlineStr"/>
-    </row>
-    <row r="53" ht="28" customHeight="1">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>Criação de legendas para posts de divulgação geral</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr"/>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>POST 01 Lançamento / POST 02 Estande / POST 03 Amanhã / POST 04 Dia do evento / POST 06 Agradecimento</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="28" customHeight="1">
-      <c r="A54" s="7" t="inlineStr">
-        <is>
-          <t>Criação de criativos para posts</t>
-        </is>
-      </c>
-      <c r="B54" s="8" t="inlineStr"/>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="E54" s="7" t="inlineStr"/>
-    </row>
-    <row r="55" ht="28" customHeight="1">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>Programação dos posts via HubSpot</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr"/>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr"/>
-    </row>
-    <row r="56" ht="28" customHeight="1">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t>Cronograma e-mails marketing de convite contatos gerais</t>
-        </is>
-      </c>
-      <c r="B56" s="8" t="inlineStr"/>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="E56" s="7" t="inlineStr"/>
-    </row>
-    <row r="57" ht="28" customHeight="1">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>Criação dos e-mails mkt de divulgação</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="inlineStr"/>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="E57" s="4" t="inlineStr"/>
-    </row>
-    <row r="58" ht="28" customHeight="1">
-      <c r="A58" s="7" t="inlineStr">
-        <is>
-          <t>Criação de lista de e-mails no HubSpot para divulgação (e-mail mkt)</t>
-        </is>
-      </c>
-      <c r="B58" s="8" t="inlineStr"/>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="D58" s="7" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="E58" s="7" t="inlineStr"/>
-    </row>
-    <row r="59" ht="28" customHeight="1">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>Enviar e-mail de alinhamento aos envolvidos do evento com as ações</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr"/>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="inlineStr"/>
-    </row>
-    <row r="60" ht="28" customHeight="1">
-      <c r="A60" s="7" t="inlineStr">
-        <is>
-          <t>Criação do E-mail mkt com agradecimento pós-evento</t>
-        </is>
-      </c>
-      <c r="B60" s="8" t="inlineStr"/>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="E60" s="7" t="inlineStr">
-        <is>
-          <t>Envio: 10/set</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="28" customHeight="1">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>Abordagem de slots SAP por SDR (Lucas/Larissa)</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr"/>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="D61" s="4" t="inlineStr">
-        <is>
-          <t>Geração de demanda</t>
-        </is>
-      </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>Gancho: demonstração ao vivo, Estande 03, 9 e 10/set</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="28" customHeight="1">
-      <c r="A62" s="7" t="inlineStr"/>
-      <c r="B62" s="8" t="inlineStr"/>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="D62" s="7" t="inlineStr"/>
-      <c r="E62" s="7" t="inlineStr"/>
-    </row>
-    <row r="63" ht="28" customHeight="1">
-      <c r="A63" s="4" t="inlineStr"/>
-      <c r="B63" s="5" t="inlineStr"/>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="D63" s="4" t="inlineStr"/>
-      <c r="E63" s="4" t="inlineStr"/>
-    </row>
-    <row r="65" ht="22" customHeight="1">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>PRÉ-EVENTO</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="18" customHeight="1">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>Atividade</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>Prazo</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>Responsável</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="inlineStr">
-        <is>
-          <t>Obs.</t>
         </is>
       </c>
     </row>
     <row r="67" ht="28" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Treinamento do time (kick off interno)</t>
-        </is>
-      </c>
-      <c r="B67" s="5" t="inlineStr">
-        <is>
-          <t>Set/1</t>
-        </is>
-      </c>
-      <c r="C67" s="6" t="inlineStr">
+          <t>Fazer card para WhatsApp para convite</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr"/>
+      <c r="C67" s="10" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -1927,24 +2021,16 @@
           <t>Fran</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>Após aprovação final do planejamento — abordagem, dor, registro, o que NÃO falar</t>
-        </is>
-      </c>
+      <c r="E67" s="4" t="inlineStr"/>
     </row>
     <row r="68" ht="28" customHeight="1">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>Ativar anúncios DOOH + Google/LinkedIn</t>
-        </is>
-      </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>07/set</t>
-        </is>
-      </c>
-      <c r="C68" s="6" t="inlineStr">
+          <t>Reunião com AEs, sócios e líderes de kickoff</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="inlineStr"/>
+      <c r="C68" s="10" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -1954,24 +2040,16 @@
           <t>Fran</t>
         </is>
       </c>
-      <c r="E68" s="7" t="inlineStr">
-        <is>
-          <t>Iniciar 1 dia antes do evento</t>
-        </is>
-      </c>
+      <c r="E68" s="7" t="inlineStr"/>
     </row>
     <row r="69" ht="28" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Credenciamento para entrega do estande</t>
-        </is>
-      </c>
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>04/set</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
+          <t>Criação de legendas para posts de divulgação geral</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr"/>
+      <c r="C69" s="10" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -1981,47 +2059,39 @@
           <t>Fran</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr"/>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>POST 01 Lançamento / POST 02 Estande / POST 03 Amanhã / POST 04 Dia / POST 06 Agradecimento</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="28" customHeight="1">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>Montar estande (4 acessos)</t>
-        </is>
-      </c>
-      <c r="B70" s="8" t="inlineStr">
-        <is>
-          <t>08/set</t>
-        </is>
-      </c>
-      <c r="C70" s="6" t="inlineStr">
+          <t>Criação de criativos para posts</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="inlineStr"/>
+      <c r="C70" s="10" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>Equipe</t>
-        </is>
-      </c>
-      <c r="E70" s="7" t="inlineStr">
-        <is>
-          <t>Retirar pulseira CAEX das 09h-14h</t>
-        </is>
-      </c>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr"/>
     </row>
     <row r="71" ht="28" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>Testar ativação / totem (offline + captura de lead)</t>
-        </is>
-      </c>
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>08/set</t>
-        </is>
-      </c>
-      <c r="C71" s="6" t="inlineStr">
+          <t>Programação dos posts via HubSpot</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr"/>
+      <c r="C71" s="10" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -2031,24 +2101,16 @@
           <t>Fran</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>Plano B: notebook com demo</t>
-        </is>
-      </c>
+      <c r="E71" s="4" t="inlineStr"/>
     </row>
     <row r="72" ht="28" customHeight="1">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>Testar QR Code e formulário HubSpot</t>
-        </is>
-      </c>
-      <c r="B72" s="8" t="inlineStr">
-        <is>
-          <t>08/set</t>
-        </is>
-      </c>
-      <c r="C72" s="6" t="inlineStr">
+          <t>Cronograma e-mails marketing de convite contatos gerais</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="inlineStr"/>
+      <c r="C72" s="10" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -2058,24 +2120,16 @@
           <t>Fran</t>
         </is>
       </c>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t>URL curta como backup</t>
-        </is>
-      </c>
+      <c r="E72" s="7" t="inlineStr"/>
     </row>
     <row r="73" ht="28" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Testar vídeo looping na TV (pen drive)</t>
-        </is>
-      </c>
-      <c r="B73" s="5" t="inlineStr">
-        <is>
-          <t>08/set</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="inlineStr">
+          <t>Criação dos e-mails mkt de divulgação</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr"/>
+      <c r="C73" s="10" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -2085,24 +2139,16 @@
           <t>Fran</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>2 pen drives — 1 de reserva</t>
-        </is>
-      </c>
+      <c r="E73" s="4" t="inlineStr"/>
     </row>
     <row r="74" ht="28" customHeight="1">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>Briefar speaker Klabin (local, horário, slides)</t>
-        </is>
-      </c>
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>08/set</t>
-        </is>
-      </c>
-      <c r="C74" s="6" t="inlineStr">
+          <t>Criação de lista de e-mails no HubSpot para divulgação (e-mail mkt)</t>
+        </is>
+      </c>
+      <c r="B74" s="8" t="inlineStr"/>
+      <c r="C74" s="10" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -2112,24 +2158,16 @@
           <t>Fran</t>
         </is>
       </c>
-      <c r="E74" s="7" t="inlineStr">
-        <is>
-          <t>Confirmar quem apresenta</t>
-        </is>
-      </c>
+      <c r="E74" s="7" t="inlineStr"/>
     </row>
     <row r="75" ht="28" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>Conferir brindes, camisetas e materiais no estande</t>
-        </is>
-      </c>
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>08/set</t>
-        </is>
-      </c>
-      <c r="C75" s="6" t="inlineStr">
+          <t>Enviar email de alinhamento aos envolvidos do evento com as ações</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr"/>
+      <c r="C75" s="10" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -2142,111 +2180,119 @@
       <c r="E75" s="4" t="inlineStr"/>
     </row>
     <row r="76" ht="28" customHeight="1">
-      <c r="A76" s="7" t="inlineStr"/>
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>Criação do E-mail mkt com agradecimento pós-evento</t>
+        </is>
+      </c>
       <c r="B76" s="8" t="inlineStr"/>
-      <c r="C76" s="6" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="D76" s="7" t="inlineStr"/>
-      <c r="E76" s="7" t="inlineStr"/>
+      <c r="C76" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>Envio: 10/set</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="28" customHeight="1">
-      <c r="A77" s="4" t="inlineStr"/>
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>Abordagem de slots SAP por SDR (Lucas/Larissa)</t>
+        </is>
+      </c>
       <c r="B77" s="5" t="inlineStr"/>
-      <c r="C77" s="6" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="D77" s="4" t="inlineStr"/>
-      <c r="E77" s="4" t="inlineStr"/>
-    </row>
-    <row r="79" ht="22" customHeight="1">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>PÓS-EVENTO</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="18" customHeight="1">
-      <c r="A80" s="3" t="inlineStr">
+      <c r="C77" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>Geração de demanda</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>Gancho: demonstração ao vivo, Estande 03, 9 e 10/set</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="28" customHeight="1">
+      <c r="A78" s="7" t="inlineStr"/>
+      <c r="B78" s="8" t="inlineStr"/>
+      <c r="C78" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr"/>
+      <c r="E78" s="7" t="inlineStr"/>
+    </row>
+    <row r="79" ht="28" customHeight="1">
+      <c r="A79" s="4" t="inlineStr"/>
+      <c r="B79" s="5" t="inlineStr"/>
+      <c r="C79" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr"/>
+      <c r="E79" s="4" t="inlineStr"/>
+    </row>
+    <row r="81" ht="22" customHeight="1">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>PRÉ-EVENTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="18" customHeight="1">
+      <c r="A82" s="3" t="inlineStr">
         <is>
           <t>Atividade</t>
         </is>
       </c>
-      <c r="B80" s="3" t="inlineStr">
+      <c r="B82" s="3" t="inlineStr">
         <is>
           <t>Prazo</t>
         </is>
       </c>
-      <c r="C80" s="3" t="inlineStr">
+      <c r="C82" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D80" s="3" t="inlineStr">
+      <c r="D82" s="3" t="inlineStr">
         <is>
           <t>Responsável</t>
         </is>
       </c>
-      <c r="E80" s="3" t="inlineStr">
+      <c r="E82" s="3" t="inlineStr">
         <is>
           <t>Obs.</t>
         </is>
       </c>
-    </row>
-    <row r="81" ht="28" customHeight="1">
-      <c r="A81" s="4" t="inlineStr">
-        <is>
-          <t>Definir processo para prospecção dos leads gerados no evento</t>
-        </is>
-      </c>
-      <c r="B81" s="5" t="inlineStr"/>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="D81" s="4" t="inlineStr">
-        <is>
-          <t>Geração de demanda</t>
-        </is>
-      </c>
-      <c r="E81" s="4" t="inlineStr"/>
-    </row>
-    <row r="82" ht="28" customHeight="1">
-      <c r="A82" s="7" t="inlineStr">
-        <is>
-          <t>Recebimento do mailing dos participantes do evento (coletores)</t>
-        </is>
-      </c>
-      <c r="B82" s="8" t="inlineStr">
-        <is>
-          <t>11/set</t>
-        </is>
-      </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="D82" s="7" t="inlineStr">
-        <is>
-          <t>Fran</t>
-        </is>
-      </c>
-      <c r="E82" s="7" t="inlineStr"/>
     </row>
     <row r="83" ht="28" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>Download do mailing EventsOnSite (estande e palestra)</t>
-        </is>
-      </c>
-      <c r="B83" s="5" t="inlineStr"/>
-      <c r="C83" s="6" t="inlineStr">
+          <t>Treinamento do time (kick off interno)</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>Set/1</t>
+        </is>
+      </c>
+      <c r="C83" s="10" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -2258,22 +2304,22 @@
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>Origens separadas por canal</t>
+          <t>Após aprovação final — abordagem, dor, registro, o que NÃO falar</t>
         </is>
       </c>
     </row>
     <row r="84" ht="28" customHeight="1">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>Consolidar leads no CRM — tag SAP-NOW-2026</t>
+          <t>Ativar anúncios DOOH + Google/LinkedIn</t>
         </is>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>D+1</t>
-        </is>
-      </c>
-      <c r="C84" s="6" t="inlineStr">
+          <t>07/set</t>
+        </is>
+      </c>
+      <c r="C84" s="10" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -2283,47 +2329,51 @@
           <t>Fran</t>
         </is>
       </c>
-      <c r="E84" s="7" t="inlineStr"/>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>Iniciar 1 dia antes do evento</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="28" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>Enviar e-mail de agradecimento personalizado</t>
+          <t>Montar estande (4 acessos)</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>D+1</t>
-        </is>
-      </c>
-      <c r="C85" s="6" t="inlineStr">
+          <t>08/set</t>
+        </is>
+      </c>
+      <c r="C85" s="10" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Fran</t>
+          <t>Equipe</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>Segmentar por dor declarada</t>
+          <t>Retirar pulseira CAEX das 09h-14h</t>
         </is>
       </c>
     </row>
     <row r="86" ht="28" customHeight="1">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>E-mail com valor (case Klabin) para leads mornos</t>
+          <t>Testar ativação / totem (offline + captura de lead)</t>
         </is>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>D+3</t>
-        </is>
-      </c>
-      <c r="C86" s="6" t="inlineStr">
+          <t>08/set</t>
+        </is>
+      </c>
+      <c r="C86" s="10" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -2333,62 +2383,78 @@
           <t>Fran</t>
         </is>
       </c>
-      <c r="E86" s="7" t="inlineStr"/>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>Plano B: notebook com demo</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="28" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>Prospecção dos participantes</t>
-        </is>
-      </c>
-      <c r="B87" s="5" t="inlineStr"/>
-      <c r="C87" s="6" t="inlineStr">
+          <t>Testar QR Code e formulário HubSpot</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>08/set</t>
+        </is>
+      </c>
+      <c r="C87" s="10" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Geração de demanda</t>
+          <t>Fran</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>SLA: 48h</t>
+          <t>URL curta como backup</t>
         </is>
       </c>
     </row>
     <row r="88" ht="28" customHeight="1">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>Ligação / WhatsApp SDR — leads sem resposta</t>
+          <t>Testar vídeo looping na TV (pen drive)</t>
         </is>
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>D+5</t>
-        </is>
-      </c>
-      <c r="C88" s="6" t="inlineStr">
+          <t>08/set</t>
+        </is>
+      </c>
+      <c r="C88" s="10" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>SDR</t>
-        </is>
-      </c>
-      <c r="E88" s="7" t="inlineStr"/>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>2 pen drives — 1 de reserva</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="28" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>E-mail resultados com avaliação</t>
-        </is>
-      </c>
-      <c r="B89" s="5" t="inlineStr"/>
-      <c r="C89" s="6" t="inlineStr">
+          <t>Briefar speaker Klabin (local, horário, slides)</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>08/set</t>
+        </is>
+      </c>
+      <c r="C89" s="10" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -2398,16 +2464,24 @@
           <t>Fran</t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr"/>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>Confirmar quem apresenta</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="28" customHeight="1">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>Report final</t>
-        </is>
-      </c>
-      <c r="B90" s="8" t="inlineStr"/>
-      <c r="C90" s="6" t="inlineStr">
+          <t>Conferir brindes, camisetas e materiais no estande</t>
+        </is>
+      </c>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t>08/set</t>
+        </is>
+      </c>
+      <c r="C90" s="10" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -2417,16 +2491,12 @@
           <t>Fran</t>
         </is>
       </c>
-      <c r="E90" s="7" t="inlineStr">
-        <is>
-          <t>Comparar com 2025</t>
-        </is>
-      </c>
+      <c r="E90" s="7" t="inlineStr"/>
     </row>
     <row r="91" ht="28" customHeight="1">
       <c r="A91" s="4" t="inlineStr"/>
       <c r="B91" s="5" t="inlineStr"/>
-      <c r="C91" s="6" t="inlineStr">
+      <c r="C91" s="10" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -2437,7 +2507,7 @@
     <row r="92" ht="28" customHeight="1">
       <c r="A92" s="7" t="inlineStr"/>
       <c r="B92" s="8" t="inlineStr"/>
-      <c r="C92" s="6" t="inlineStr">
+      <c r="C92" s="10" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
@@ -2445,14 +2515,296 @@
       <c r="D92" s="7" t="inlineStr"/>
       <c r="E92" s="7" t="inlineStr"/>
     </row>
+    <row r="94" ht="22" customHeight="1">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>PÓS-EVENTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="18" customHeight="1">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>Atividade</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>Prazo</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>Responsável</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>Obs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="28" customHeight="1">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>Definir processo para prospecção dos leads gerados no evento</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="inlineStr"/>
+      <c r="C96" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>Geração de demanda</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr"/>
+    </row>
+    <row r="97" ht="28" customHeight="1">
+      <c r="A97" s="7" t="inlineStr">
+        <is>
+          <t>Recebimento do mailing dos participantes do evento (coletores)</t>
+        </is>
+      </c>
+      <c r="B97" s="8" t="inlineStr">
+        <is>
+          <t>11/set</t>
+        </is>
+      </c>
+      <c r="C97" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr"/>
+    </row>
+    <row r="98" ht="28" customHeight="1">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>Download do mailing EventsOnSite (estande e palestra)</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="inlineStr"/>
+      <c r="C98" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>Origens separadas por canal</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="28" customHeight="1">
+      <c r="A99" s="7" t="inlineStr">
+        <is>
+          <t>Consolidar leads no CRM — tag SAP-NOW-2026</t>
+        </is>
+      </c>
+      <c r="B99" s="8" t="inlineStr">
+        <is>
+          <t>D+1</t>
+        </is>
+      </c>
+      <c r="C99" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr"/>
+    </row>
+    <row r="100" ht="28" customHeight="1">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>Enviar e-mail de agradecimento personalizado</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>D+1</t>
+        </is>
+      </c>
+      <c r="C100" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>Segmentar por dor declarada</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="28" customHeight="1">
+      <c r="A101" s="7" t="inlineStr">
+        <is>
+          <t>E-mail com valor (case Klabin) para leads mornos</t>
+        </is>
+      </c>
+      <c r="B101" s="8" t="inlineStr">
+        <is>
+          <t>D+3</t>
+        </is>
+      </c>
+      <c r="C101" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="E101" s="7" t="inlineStr"/>
+    </row>
+    <row r="102" ht="28" customHeight="1">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>Prospecção dos participantes</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="inlineStr"/>
+      <c r="C102" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>Geração de demanda</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>SLA: 48h</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="28" customHeight="1">
+      <c r="A103" s="7" t="inlineStr">
+        <is>
+          <t>Ligação / WhatsApp SDR — leads sem resposta</t>
+        </is>
+      </c>
+      <c r="B103" s="8" t="inlineStr">
+        <is>
+          <t>D+5</t>
+        </is>
+      </c>
+      <c r="C103" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>SDR</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="inlineStr"/>
+    </row>
+    <row r="104" ht="28" customHeight="1">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>E-mail resultados com avaliação</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="inlineStr"/>
+      <c r="C104" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr"/>
+    </row>
+    <row r="105" ht="28" customHeight="1">
+      <c r="A105" s="7" t="inlineStr">
+        <is>
+          <t>Report final</t>
+        </is>
+      </c>
+      <c r="B105" s="8" t="inlineStr"/>
+      <c r="C105" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="inlineStr">
+        <is>
+          <t>Comparar com 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="28" customHeight="1">
+      <c r="A106" s="4" t="inlineStr"/>
+      <c r="B106" s="5" t="inlineStr"/>
+      <c r="C106" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr"/>
+      <c r="E106" s="4" t="inlineStr"/>
+    </row>
+    <row r="107" ht="28" customHeight="1">
+      <c r="A107" s="7" t="inlineStr"/>
+      <c r="B107" s="8" t="inlineStr"/>
+      <c r="C107" s="10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="D107" s="7" t="inlineStr"/>
+      <c r="E107" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:E93"/>
+  <autoFilter ref="A2:E108"/>
   <mergeCells count="5">
-    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A81:E81"/>
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A94:E94"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A45:E45"/>
-    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A61:E61"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2472,7 +2824,7 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -2525,7 +2877,7 @@
           <t>RedDoor</t>
         </is>
       </c>
-      <c r="C3" s="9" t="n">
+      <c r="C3" s="11" t="n">
         <v>265000</v>
       </c>
       <c r="D3" s="7" t="inlineStr"/>
@@ -2533,22 +2885,22 @@
       <c r="F3" s="7" t="inlineStr"/>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Cota extra de comunicação</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C4" s="11" t="n">
+      <c r="C4" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="10" t="inlineStr"/>
-      <c r="E4" s="10" t="inlineStr"/>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr"/>
+      <c r="E4" s="12" t="inlineStr"/>
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>A confirmar se aplica</t>
         </is>
@@ -2565,7 +2917,7 @@
           <t>RedDoor</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="11" t="n">
         <v>1601.14</v>
       </c>
       <c r="D5" s="7" t="inlineStr"/>
@@ -2577,22 +2929,22 @@
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Brindes — Cubo Mágico (250 un.)</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>A Cuber Brasil</t>
         </is>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="14" t="n">
         <v>10407.5</v>
       </c>
-      <c r="D6" s="10" t="inlineStr"/>
-      <c r="E6" s="10" t="inlineStr"/>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr"/>
+      <c r="E6" s="12" t="inlineStr"/>
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>R$ 41,63/un — UV direto 5,6cm — renan@cuberbrasil.com / (19) 99606-4010</t>
         </is>
@@ -2601,7 +2953,7 @@
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Brindes — Bloco notas cubo BL31 (250)</t>
+          <t>Brindes — Bloco notas cubo BL31 (250 un.)</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -2609,34 +2961,34 @@
           <t>A definir</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="11" t="n">
         <v>8767.5</v>
       </c>
       <c r="D7" s="7" t="inlineStr"/>
       <c r="E7" s="7" t="inlineStr"/>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>R$ 35,07/un — 95x95mm, sik screen, azul</t>
+          <t>R$ 35,07/un — 95x95x95mm, sik screen, azul</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Camisetas e polos</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>A contratar</t>
         </is>
       </c>
-      <c r="C8" s="11" t="n">
+      <c r="C8" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="10" t="inlineStr"/>
-      <c r="E8" s="10" t="inlineStr"/>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr"/>
+      <c r="E8" s="12" t="inlineStr"/>
+      <c r="F8" s="12" t="inlineStr">
         <is>
           <t>27 camisetas + 12 polos — aguardando RH</t>
         </is>
@@ -2653,7 +3005,7 @@
           <t>Eletromidia</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="11" t="n">
         <v>4988.69</v>
       </c>
       <c r="D9" s="7" t="inlineStr"/>
@@ -2665,22 +3017,22 @@
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>Vídeos (looping + cases)</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>A contratar</t>
         </is>
       </c>
-      <c r="C10" s="12" t="n">
+      <c r="C10" s="14" t="n">
         <v>5280</v>
       </c>
-      <c r="D10" s="10" t="inlineStr"/>
-      <c r="E10" s="10" t="inlineStr"/>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr"/>
+      <c r="E10" s="12" t="inlineStr"/>
+      <c r="F10" s="12" t="inlineStr">
         <is>
           <t>SAP com LCA estará no evento</t>
         </is>
@@ -2697,34 +3049,34 @@
           <t>Kalunga</t>
         </is>
       </c>
-      <c r="C11" s="13" t="n">
+      <c r="C11" s="15" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="7" t="inlineStr"/>
       <c r="E11" s="7" t="inlineStr"/>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>Impressão de arte para display — a orçar</t>
+          <t>A orçar</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>Arte do estande (agência)</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>A contratar</t>
         </is>
       </c>
-      <c r="C12" s="11" t="n">
+      <c r="C12" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="10" t="inlineStr"/>
-      <c r="E12" s="10" t="inlineStr"/>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr"/>
+      <c r="E12" s="12" t="inlineStr"/>
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t>Trainel + Painel + Balcão — a orçar</t>
         </is>
@@ -2741,7 +3093,7 @@
           <t>A contratar</t>
         </is>
       </c>
-      <c r="C13" s="13" t="n">
+      <c r="C13" s="15" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="7" t="inlineStr"/>
@@ -2753,22 +3105,22 @@
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>LinkedIn Ads + Google Ads</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>A contratar</t>
         </is>
       </c>
-      <c r="C14" s="11" t="n">
+      <c r="C14" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="10" t="inlineStr"/>
-      <c r="E14" s="10" t="inlineStr"/>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr"/>
+      <c r="E14" s="12" t="inlineStr"/>
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>Geolocalização 07-11/set — a orçar</t>
         </is>
@@ -2785,7 +3137,7 @@
           <t>A contratar</t>
         </is>
       </c>
-      <c r="C15" s="13" t="n">
+      <c r="C15" s="15" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="7" t="inlineStr"/>
@@ -2802,7 +3154,7 @@
           <t>TOTAL PARCIAL (itens com valor preenchido)</t>
         </is>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="16">
         <f>SUM(C3:C15)</f>
         <v/>
       </c>
@@ -2833,7 +3185,7 @@
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="48" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -2919,10 +3271,10 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="G3" s="9" t="n">
+      <c r="G3" s="11" t="n">
         <v>19.1</v>
       </c>
-      <c r="H3" s="9" t="n">
+      <c r="H3" s="11" t="n">
         <v>4775</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
@@ -2932,123 +3284,123 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Cubo mágico personalizado (5,5x5,5cm)</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>Imprimus</t>
         </is>
       </c>
-      <c r="C4" s="15" t="n">
+      <c r="C4" s="17" t="n">
         <v>250</v>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" s="17" t="inlineStr">
         <is>
           <t>15 dias</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr">
+      <c r="F4" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="12" t="n">
+      <c r="G4" s="14" t="n">
         <v>13.95</v>
       </c>
-      <c r="H4" s="12" t="n">
+      <c r="H4" s="14" t="n">
         <v>3487.5</v>
       </c>
-      <c r="I4" s="10" t="inlineStr">
+      <c r="I4" s="12" t="inlineStr">
         <is>
           <t>Gravação Offset — guilherme@imprimus.com.br / (19) 3245-1615</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
-        <is>
-          <t>Cubo Mágico Profissional 3x3x3 (5,6cm)  ✓</t>
-        </is>
-      </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>Cubo Mágico Profissional 3x3x3 (5,6cm)  ✓ ESCOLHIDO</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>A Cuber Brasil</t>
         </is>
       </c>
-      <c r="C5" s="17" t="n">
+      <c r="C5" s="19" t="n">
         <v>250</v>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="E5" s="17" t="inlineStr">
+      <c r="E5" s="19" t="inlineStr">
         <is>
           <t>4 dias</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="18" t="n">
+      <c r="G5" s="20" t="n">
         <v>41.63</v>
       </c>
-      <c r="H5" s="18" t="n">
+      <c r="H5" s="20" t="n">
         <v>10407.5</v>
       </c>
-      <c r="I5" s="16" t="inlineStr">
+      <c r="I5" s="18" t="inlineStr">
         <is>
           <t>UV direto no material — renan@cuberbrasil.com / (19) 99606-4010</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Cubo mágico 5,5x5,5x5,5</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>ESP Brindes</t>
         </is>
       </c>
-      <c r="C6" s="15" t="n">
+      <c r="C6" s="17" t="n">
         <v>250</v>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>15 dias</t>
         </is>
       </c>
-      <c r="F6" s="15" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>CIF</t>
         </is>
       </c>
-      <c r="G6" s="12" t="n">
+      <c r="G6" s="14" t="n">
         <v>18.4</v>
       </c>
-      <c r="H6" s="12" t="n">
+      <c r="H6" s="14" t="n">
         <v>4600</v>
       </c>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="I6" s="12" t="inlineStr">
         <is>
           <t>Papel adesivo com brilho envernizado — contato@espbrindes.com.br</t>
         </is>
@@ -3083,10 +3435,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="9" t="n">
+      <c r="G7" s="11" t="n">
         <v>35.07</v>
       </c>
-      <c r="H7" s="9" t="n">
+      <c r="H7" s="11" t="n">
         <v>8767.5</v>
       </c>
       <c r="I7" s="7" t="inlineStr">
@@ -3096,41 +3448,41 @@
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Cubo Mágico Profissional 3x3x3 (5,6cm)</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>Still Promotion</t>
         </is>
       </c>
-      <c r="C8" s="15" t="n">
+      <c r="C8" s="17" t="n">
         <v>250</v>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="E8" s="15" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>A combinar</t>
         </is>
       </c>
-      <c r="F8" s="15" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>CIF</t>
         </is>
       </c>
-      <c r="G8" s="12" t="n">
+      <c r="G8" s="14" t="n">
         <v>66.90000000000001</v>
       </c>
-      <c r="H8" s="12" t="n">
+      <c r="H8" s="14" t="n">
         <v>16725</v>
       </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="I8" s="12" t="inlineStr">
         <is>
           <t>UV direto no material — fabio@stillpromotion.com.br / 11-3906-0300</t>
         </is>

--- a/eventos/sap-now-2026/checklist-sap-now-2026.xlsx
+++ b/eventos/sap-now-2026/checklist-sap-now-2026.xlsx
@@ -936,15 +936,19 @@
           <t>06/jun</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>Em andamento</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr"/>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Ok</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>Klabin, enviar para a SAP</t>
+          <t>Enviado para aprovação SAP em 10/06/26 — aguardando confirmação</t>
         </is>
       </c>
     </row>
@@ -1193,9 +1197,9 @@
           <t>26/jun</t>
         </is>
       </c>
-      <c r="C28" s="10" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Ok</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -1205,7 +1209,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>CRÍTICO — prazo fixo SAP</t>
+          <t>Enviado em 10/06/26 — Klabin (BDC) e Ourofino (BDC + Planning)</t>
         </is>
       </c>
     </row>
